--- a/tables/water/phytoplankton_parameters.xlsx
+++ b/tables/water/phytoplankton_parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matthipsey/AED Dropbox/Matt Hipsey/GitHub/cdm-science/tables/water/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/AED5/AED Dropbox/AED_Cockburn_db/SEAF-CS/csiem-science/tables/water/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC1191E-DE6B-2D4E-9334-FDBFEC6818A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9654ED84-2472-6A4E-AFD1-6414B7490A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="13720" yWindow="1780" windowWidth="28680" windowHeight="26180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,18 +438,6 @@
     <t>Silica</t>
   </si>
   <si>
-    <t>Parameter1</t>
-  </si>
-  <si>
-    <t>Parameter2</t>
-  </si>
-  <si>
-    <t>Parameter3</t>
-  </si>
-  <si>
-    <t>Parameter4</t>
-  </si>
-  <si>
     <t>Group</t>
   </si>
   <si>
@@ -505,6 +493,18 @@
   </si>
   <si>
     <t>…</t>
+  </si>
+  <si>
+    <t>PFT1</t>
+  </si>
+  <si>
+    <t>PFT2</t>
+  </si>
+  <si>
+    <t>PFT3</t>
+  </si>
+  <si>
+    <t>PFT4</t>
   </si>
 </sst>
 </file>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>10</v>
@@ -970,16 +970,16 @@
         <v>2</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="23" customHeight="1" x14ac:dyDescent="0.2">
@@ -2492,16 +2492,16 @@
     </row>
     <row r="54" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E54" s="13" t="s">
         <v>22</v>
@@ -2512,16 +2512,16 @@
     </row>
     <row r="55" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D55" s="12" t="s">
         <v>142</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>146</v>
       </c>
       <c r="E55" s="13" t="s">
         <v>22</v>
@@ -2532,16 +2532,16 @@
     </row>
     <row r="56" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E56" s="13" t="s">
         <v>22</v>
@@ -2552,13 +2552,13 @@
     </row>
     <row r="57" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D57" s="12" t="s">
         <v>37</v>
@@ -2572,19 +2572,19 @@
     </row>
     <row r="58" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F58" s="14">
         <v>1500</v>
@@ -2592,16 +2592,16 @@
     </row>
     <row r="59" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E59" s="13" t="s">
         <v>7</v>
@@ -2612,16 +2612,16 @@
     </row>
     <row r="60" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E60" s="13" t="s">
         <v>7</v>
@@ -2632,22 +2632,22 @@
     </row>
     <row r="61" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A61" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E61" s="13" t="s">
         <v>7</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/tables/water/phytoplankton_parameters.xlsx
+++ b/tables/water/phytoplankton_parameters.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/AED5/AED Dropbox/AED_Cockburn_db/SEAF-CS/csiem-science/tables/water/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/00042030/AED Dropbox/AED_Cockburn_db/SEAF-CS/csiem-science/tables/water/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9654ED84-2472-6A4E-AFD1-6414B7490A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061EB051-FAFA-384E-ACD7-627352297F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13720" yWindow="1780" windowWidth="28680" windowHeight="26180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="640" yWindow="2320" windowWidth="28700" windowHeight="18040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="aed_phytoplankton" sheetId="1" r:id="rId1"/>
+    <sheet name="aed_light" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="185">
   <si>
     <t>Table</t>
   </si>
@@ -505,13 +506,88 @@
   </si>
   <si>
     <t>PFT4</t>
+  </si>
+  <si>
+    <t>Specific Attenuation</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>K_w</t>
+  </si>
+  <si>
+    <t>m^{-1}</t>
+  </si>
+  <si>
+    <t>POC optical effects vary by composition; equivalent to $0.001–0.01 \: m^2 mg C^{-1}$. For mmol C units, this corresponds approximately to $0.012–0.12\: m^2 mmol C^{-1}$ (using 1 mmol C ≈ 12 mg C).</t>
+  </si>
+  <si>
+    <t>Background water attenuation typically 0.04–0.07 in clear coastal waters.</t>
+  </si>
+  <si>
+    <t>Pure water attenuation</t>
+  </si>
+  <si>
+    <t>k_{e_{ss1}}</t>
+  </si>
+  <si>
+    <t>k_{e_{phy}}</t>
+  </si>
+  <si>
+    <t>k_{e_{doc}}</t>
+  </si>
+  <si>
+    <t>k_{e_{poc}}</t>
+  </si>
+  <si>
+    <t>k_{e_{ss2}}</t>
+  </si>
+  <si>
+    <t>CSIEM</t>
+  </si>
+  <si>
+    <t>0.0030 - 0.0051 (group specific)</t>
+  </si>
+  <si>
+    <t>Attenuation by $CDOM$ (as indicated by $DOC$)</t>
+  </si>
+  <si>
+    <t>Attenuation by detritus ($POC$)</t>
+  </si>
+  <si>
+    <t>Attenuation by coarse SS group ($SS_2$)</t>
+  </si>
+  <si>
+    <t>Attenuation by fine SS group ($SS_1$)</t>
+  </si>
+  <si>
+    <t>Attenuation by $\text{Chl-a}$ (as indicated by $PHY_C$)</t>
+  </si>
+  <si>
+    <t>Fine suspended sediments: 0.05–0.15; higher attenuation rates for fine silts and clays with strong scattering properties.</t>
+  </si>
+  <si>
+    <t>Coarser inorganic particles (fine sands and silt): $0.02–0.06$; attenuation drops with increasing particle size as less scattering per unit mass (Bowers &amp; Binding 2006). Default value of $0.05$ commonly adopted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> This term is usually elevated near riverine or groundwater inputs with high terrestrial DOM inputs. DOC influences light via CDOM absorption. Typical coastal CDOM attenuation 0.001–0.02 m\(^2\) mg C\(^{-1}\), equivalent to 0.012–0.240 m\(^2\) mmol C\(^{-1}\).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This term influences extinction due to algal biomass. Phytoplankton chlorophyll-specific attenuation values reported between $0.015–0.03\:m^2\:mg\:\text{Chl-a}^{-1}$ (Gallegos 2001; Gallegos and Moore 2000; Devlin et al. 2009), with ~0.02 commonly used. In carbon units (for AED), this equates to $0.0036–0.0072 \: m^{-1}/ (mmol\:C/m^{-3})^{-1}$. O2M (2025) estimated phytoplankton attenuation locally with Cockburn Sound data from March 2025 and estimated $K_{e_{chla}}$ to be $$K_{e_{phy}} = 0.128\: m^2\: mg\:\text{Chl-a}\:^{-1}$ which converts to $~0.03\: m^{-1} (mmol\:C/m^{-3})^{-1}$ </t>
+  </si>
+  <si>
+    <t>m^{-1}\:(g\:m^{-3})^{-1}</t>
+  </si>
+  <si>
+    <t>m^{-1}\:(mmol\:C\:m^{-3})^{-1}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -543,8 +619,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -575,8 +668,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -623,11 +722,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -663,6 +795,31 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2653,4 +2810,180 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C0AEBD1-3A36-2649-A295-D94950BC717E}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.1640625" customWidth="1"/>
+    <col min="7" max="7" width="89.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="F2" s="25">
+        <v>0.05</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="25">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="G3" s="25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="F4" s="25">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" s="25">
+        <v>0.01</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" s="25">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>182</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tables/water/phytoplankton_parameters.xlsx
+++ b/tables/water/phytoplankton_parameters.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="433">
   <si>
     <t>Table</t>
   </si>
@@ -1307,6 +1307,12 @@
   </si>
   <si>
     <t xml:space="preserve">temperature multiplier for MPB respiration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">see Appendix B</t>
   </si>
 </sst>
 </file>
@@ -1330,11 +1336,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -1344,6 +1345,11 @@
       <name val="Calibri"/>
       <b/>
       <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1374,12 +1380,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -1387,6 +1387,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1474,34 +1480,34 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1514,19 +1520,19 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1824,1553 +1830,1553 @@
       <c r="B1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="D1" s="13" t="s">
+      <c r="C1" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="2" ht="23" customHeight="1">
-      <c r="A2" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="14" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="3" ht="23" customHeight="1">
-      <c r="A3" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B3" s="14" t="s">
+      <c r="A3" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="14" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1">
-      <c r="A4" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="14" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
-      <c r="A5" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="14" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
-      <c r="A6" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B6" s="14" t="s">
+      <c r="A6" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="14" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="7" ht="23" customHeight="1">
-      <c r="A7" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B7" s="14" t="s">
+      <c r="A7" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="14" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="8" ht="23" customHeight="1">
-      <c r="A8" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B8" s="14" t="s">
+      <c r="A8" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="14" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="9" ht="23" customHeight="1">
-      <c r="A9" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B9" s="14" t="s">
+      <c r="A9" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="14" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="10" ht="23" customHeight="1">
-      <c r="A10" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B10" s="14" t="s">
+      <c r="A10" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="14" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="11" ht="23" customHeight="1">
-      <c r="A11" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B11" s="14" t="s">
+      <c r="A11" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="14" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="12" ht="23" customHeight="1">
-      <c r="A12" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B12" s="14" t="s">
+      <c r="A12" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I12" s="4" t="s">
+      <c r="F12" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="I12" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="13" ht="23" customHeight="1">
-      <c r="A13" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B13" s="14" t="s">
+      <c r="A13" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="14" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="14" ht="23" customHeight="1">
-      <c r="A14" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B14" s="14" t="s">
+      <c r="A14" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="14" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="15" ht="23" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B15" s="14" t="s">
+      <c r="A15" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="14" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="16" ht="23" customHeight="1">
-      <c r="A16" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="14" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1">
-      <c r="A17" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B17" s="14" t="s">
+      <c r="A17" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="14" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1">
-      <c r="A18" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="14" t="s">
+      <c r="A18" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="14" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
-      <c r="A19" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B19" s="14" t="s">
+      <c r="A19" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="14" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
-      <c r="A20" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B20" s="14" t="s">
+      <c r="A20" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="14" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
-      <c r="A21" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B21" s="14" t="s">
+      <c r="A21" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="14" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
-      <c r="A22" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B22" s="14" t="s">
+      <c r="A22" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="12" t="s">
         <v>283</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="14" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
-      <c r="A23" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B23" s="14" t="s">
+      <c r="A23" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="14" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
-      <c r="A24" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B24" s="14" t="s">
+      <c r="A24" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="14" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
-      <c r="A25" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B25" s="14" t="s">
+      <c r="A25" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I25" s="4" t="s">
+      <c r="F25" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="I25" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
-      <c r="A26" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B26" s="14" t="s">
+      <c r="A26" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I26" s="4" t="s">
+      <c r="F26" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="I26" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
-      <c r="A27" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B27" s="14" t="s">
+      <c r="A27" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I27" s="4" t="s">
+      <c r="F27" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="I27" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
-      <c r="A28" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B28" s="14" t="s">
+      <c r="A28" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="14" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
-      <c r="A29" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B29" s="14" t="s">
+      <c r="A29" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="14" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
-      <c r="A30" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B30" s="14" t="s">
+      <c r="A30" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="14" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
-      <c r="A31" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B31" s="14" t="s">
+      <c r="A31" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="14" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
-      <c r="A32" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B32" s="14" t="s">
+      <c r="A32" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" s="14" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
-      <c r="A33" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B33" s="14" t="s">
+      <c r="A33" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" s="14" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
-      <c r="A34" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B34" s="14" t="s">
+      <c r="A34" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="12" t="s">
         <v>328</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="14" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
-      <c r="A35" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B35" s="14" t="s">
+      <c r="A35" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B35" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="14" t="s">
         <v>332</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="I35" s="4" t="s">
+      <c r="I35" s="14" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
-      <c r="A36" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B36" s="14" t="s">
+      <c r="A36" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" s="14" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
-      <c r="A37" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B37" s="14" t="s">
+      <c r="A37" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B37" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="D37" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I37" s="4" t="s">
+      <c r="F37" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="I37" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
-      <c r="A38" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B38" s="14" t="s">
+      <c r="A38" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B38" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="13" t="s">
         <v>338</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="I38" s="14" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
-      <c r="A39" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B39" s="14" t="s">
+      <c r="A39" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="H39" s="4" t="s">
+      <c r="H39" s="14" t="s">
         <v>345</v>
       </c>
-      <c r="I39" s="4" t="s">
+      <c r="I39" s="14" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
-      <c r="A40" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B40" s="14" t="s">
+      <c r="A40" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B40" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="12" t="s">
         <v>346</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="14" t="s">
         <v>348</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="14" t="s">
         <v>349</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I40" s="14" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
-      <c r="A41" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B41" s="14" t="s">
+      <c r="A41" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B41" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="D41" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="H41" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="I41" s="4" t="s">
+      <c r="I41" s="14" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
-      <c r="A42" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B42" s="14" t="s">
+      <c r="A42" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B42" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="D42" s="3" t="s">
+      <c r="D42" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="14" t="s">
         <v>339</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H42" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="I42" s="4" t="s">
+      <c r="I42" s="14" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
-      <c r="A43" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B43" s="14" t="s">
+      <c r="A43" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B43" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="14" t="s">
         <v>362</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H43" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="I43" s="4" t="s">
+      <c r="I43" s="14" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
-      <c r="A44" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B44" s="14" t="s">
+      <c r="A44" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B44" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I44" s="4" t="s">
+      <c r="F44" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="I44" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
-      <c r="A45" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B45" s="14" t="s">
+      <c r="A45" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B45" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I45" s="4" t="s">
+      <c r="F45" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="I45" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
-      <c r="A46" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B46" s="14" t="s">
+      <c r="A46" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B46" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="H46" s="4" t="s">
+      <c r="H46" s="14" t="s">
         <v>375</v>
       </c>
-      <c r="I46" s="4" t="s">
+      <c r="I46" s="14" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
-      <c r="A47" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B47" s="14" t="s">
+      <c r="A47" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="12" t="s">
         <v>376</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="D47" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H47" s="14" t="s">
         <v>380</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="I47" s="14" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
-      <c r="A48" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B48" s="14" t="s">
+      <c r="A48" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B48" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="H48" s="14" t="s">
         <v>387</v>
       </c>
-      <c r="I48" s="4" t="s">
+      <c r="I48" s="14" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
-      <c r="A49" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B49" s="14" t="s">
+      <c r="A49" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B49" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I49" s="4" t="s">
+      <c r="F49" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="I49" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
-      <c r="A50" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B50" s="14" t="s">
+      <c r="A50" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B50" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="12" t="s">
         <v>392</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I50" s="4" t="s">
+      <c r="F50" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="I50" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
-      <c r="A51" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B51" s="14" t="s">
+      <c r="A51" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B51" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="13" t="s">
         <v>396</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I51" s="4" t="s">
+      <c r="F51" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G51" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="I51" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="52" ht="23" customHeight="1">
-      <c r="A52" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B52" s="14" t="s">
+      <c r="A52" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B52" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I52" s="4" t="s">
+      <c r="F52" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="I52" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="53" ht="23" customHeight="1">
-      <c r="A53" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="B53" s="14" t="s">
+      <c r="A53" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B53" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="12" t="s">
         <v>399</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="D53" s="13" t="s">
         <v>400</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I53" s="4" t="s">
+      <c r="F53" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="H53" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="I53" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="7" t="s">
+      <c r="A54" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="5" t="s">
         <v>402</v>
       </c>
-      <c r="D54" s="9" t="s">
+      <c r="D54" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="8" t="s">
         <v>421</v>
       </c>
       <c r="G54"/>
@@ -3378,22 +3384,22 @@
       <c r="I54"/>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="8" t="s">
         <v>422</v>
       </c>
       <c r="G55"/>
@@ -3401,22 +3407,22 @@
       <c r="I55"/>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="8" t="s">
         <v>423</v>
       </c>
       <c r="G56"/>
@@ -3424,22 +3430,22 @@
       <c r="I56"/>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D57" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="8" t="s">
         <v>424</v>
       </c>
       <c r="G57"/>
@@ -3447,22 +3453,22 @@
       <c r="I57"/>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="D58" s="9" t="s">
+      <c r="D58" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="8" t="s">
         <v>425</v>
       </c>
       <c r="G58"/>
@@ -3470,22 +3476,22 @@
       <c r="I58"/>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="7" t="s">
+      <c r="A59" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="D59" s="9" t="s">
+      <c r="D59" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="8" t="s">
         <v>428</v>
       </c>
       <c r="G59"/>
@@ -3493,22 +3499,22 @@
       <c r="I59"/>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="8" t="s">
         <v>428</v>
       </c>
       <c r="G60"/>
@@ -3516,22 +3522,22 @@
       <c r="I60"/>
     </row>
     <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="5" t="s">
         <v>414</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D61" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="8" t="s">
         <v>304</v>
       </c>
       <c r="G61"/>
@@ -3578,7 +3584,7 @@
         <v>197</v>
       </c>
       <c r="F63" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
